--- a/src/main/resources/baseFiles/excel/filteredCollectedContacts.xlsx
+++ b/src/main/resources/baseFiles/excel/filteredCollectedContacts.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13580"/>
+    <workbookView windowWidth="27660" windowHeight="12000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10419" uniqueCount="5073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11409" uniqueCount="5474">
   <si>
     <t>Min-Tae Kim</t>
   </si>
@@ -15248,6 +15248,1209 @@
   </si>
   <si>
     <t>pawarisa.s@zicoip.com</t>
+  </si>
+  <si>
+    <t>Cheng Zhong</t>
+  </si>
+  <si>
+    <t>chengzhong@tongshang.com</t>
+  </si>
+  <si>
+    <t>tel:+86 21 6019 2600</t>
+  </si>
+  <si>
+    <t>https://www.tongshang.com/Professionals/ChengZhong.html</t>
+  </si>
+  <si>
+    <t>Partner </t>
+  </si>
+  <si>
+    <t>Cui Qiang</t>
+  </si>
+  <si>
+    <t>cuiqiang@tongshang.com</t>
+  </si>
+  <si>
+    <t>Commercial litigation,</t>
+  </si>
+  <si>
+    <t>https://www.tongshang.com/Professionals/CuiQiang.html</t>
+  </si>
+  <si>
+    <t>Deng Xiaomeng</t>
+  </si>
+  <si>
+    <t>dengxiaomeng@tongshang.com</t>
+  </si>
+  <si>
+    <t>investment funds in real</t>
+  </si>
+  <si>
+    <t>https://www.tongshang.com/Professionals/DengXiaoMeng.html</t>
+  </si>
+  <si>
+    <t>Guo Xiaoming</t>
+  </si>
+  <si>
+    <t>guoxiaoming@tongshang.com</t>
+  </si>
+  <si>
+    <t>tel:+86 755 8351 7570</t>
+  </si>
+  <si>
+    <t>Compliance and government</t>
+  </si>
+  <si>
+    <t>https://www.tongshang.com/Professionals/GuoXiaoMing.html</t>
+  </si>
+  <si>
+    <t>Hou Qinghai</t>
+  </si>
+  <si>
+    <t>houqinghai@tongshang.com</t>
+  </si>
+  <si>
+    <t>https://www.tongshang.com/Professionals/HouQingHai.html</t>
+  </si>
+  <si>
+    <t>Charles Xu</t>
+  </si>
+  <si>
+    <t>c.xu@dandreapartners.com</t>
+  </si>
+  <si>
+    <t>Corporate Compliance Services</t>
+  </si>
+  <si>
+    <t>https://www.dandreapartners.com/member/charles-xu/</t>
+  </si>
+  <si>
+    <t>D'Andrea &amp; Partners</t>
+  </si>
+  <si>
+    <t>Landon He</t>
+  </si>
+  <si>
+    <t>l.he@dandreapartners.com</t>
+  </si>
+  <si>
+    <t>tel:021 62187350</t>
+  </si>
+  <si>
+    <t>company law</t>
+  </si>
+  <si>
+    <t>https://www.dandreapartners.com/member/landon-he/</t>
+  </si>
+  <si>
+    <t>Roberto Saccoccia</t>
+  </si>
+  <si>
+    <t>r.saccoccia@dandreapartners.com</t>
+  </si>
+  <si>
+    <t>tel:+39 0852121032</t>
+  </si>
+  <si>
+    <t>commercial and criminal law</t>
+  </si>
+  <si>
+    <t>https://www.dandreapartners.com/member/roberto-saccoccia/</t>
+  </si>
+  <si>
+    <t>Tran Si Vy</t>
+  </si>
+  <si>
+    <t>v.tran@dandreapartners.com</t>
+  </si>
+  <si>
+    <t>tel:+84 439425633/111</t>
+  </si>
+  <si>
+    <t>https://www.dandreapartners.com/member/tran-si-vy/</t>
+  </si>
+  <si>
+    <t>Salvatore Banco</t>
+  </si>
+  <si>
+    <t>s.banco@dandreapartners.com</t>
+  </si>
+  <si>
+    <t>manufacturing to IT</t>
+  </si>
+  <si>
+    <t>https://www.dandreapartners.com/member/salvatore-banco/</t>
+  </si>
+  <si>
+    <t>Head of Ho Chi Minh City &amp; South China Offices</t>
+  </si>
+  <si>
+    <t>Christie Liu</t>
+  </si>
+  <si>
+    <t>commercial litigation,</t>
+  </si>
+  <si>
+    <t>https://www.rs-lawyers.com.hk/team/christie-liu</t>
+  </si>
+  <si>
+    <t>RS Lawyers</t>
+  </si>
+  <si>
+    <t>regulation and compliance risks</t>
+  </si>
+  <si>
+    <t>WANG, Xuying</t>
+  </si>
+  <si>
+    <t>wangxuying@haiwen-law.com</t>
+  </si>
+  <si>
+    <t>tel:(+86 10) 8564 0728</t>
+  </si>
+  <si>
+    <t>http://www.haiwen-law.com/64/306</t>
+  </si>
+  <si>
+    <t>Hai Wen</t>
+  </si>
+  <si>
+    <t>TANG, Xue</t>
+  </si>
+  <si>
+    <t>tangxue@haiwen-law.com</t>
+  </si>
+  <si>
+    <t>tel: (+86 21) 6043 5058</t>
+  </si>
+  <si>
+    <t>http://www.haiwen-law.com/64/32</t>
+  </si>
+  <si>
+    <t>GAO, Xiaomin</t>
+  </si>
+  <si>
+    <t>gaoxiaomin@haiwen-law.com</t>
+  </si>
+  <si>
+    <t>（+86 755）8323 6413</t>
+  </si>
+  <si>
+    <t>http://www.haiwen-law.com/64/290</t>
+  </si>
+  <si>
+    <t>FAN, Haiwei</t>
+  </si>
+  <si>
+    <t>fanhaiwei@haiwen-law.com</t>
+  </si>
+  <si>
+    <t>(+86 10) 8560 6837</t>
+  </si>
+  <si>
+    <t>http://www.haiwen-law.com/64/288</t>
+  </si>
+  <si>
+    <t>Yolanda JIA</t>
+  </si>
+  <si>
+    <t>jiayuanyuan@haiwen-law.com</t>
+  </si>
+  <si>
+    <t>tel:(+86 10) 5089 2232</t>
+  </si>
+  <si>
+    <t>http://www.haiwen-law.com/64/213</t>
+  </si>
+  <si>
+    <t>Junhao Chen</t>
+  </si>
+  <si>
+    <t>chenjunhao@anlilaw.com</t>
+  </si>
+  <si>
+    <t>86 21 6289 8808</t>
+  </si>
+  <si>
+    <t>Intellectual property</t>
+  </si>
+  <si>
+    <t>https://www.anlilaw.com/100043/1910</t>
+  </si>
+  <si>
+    <t>Anli Partners</t>
+  </si>
+  <si>
+    <t>Peng Chengxiang</t>
+  </si>
+  <si>
+    <t>jerrypeng@jchlaw.com.tw</t>
+  </si>
+  <si>
+    <t>tel:+886225638900</t>
+  </si>
+  <si>
+    <t>white-collar crime cases</t>
+  </si>
+  <si>
+    <t>https://www.jchlaw.com.tw/about/17.htm</t>
+  </si>
+  <si>
+    <t>JCH Law</t>
+  </si>
+  <si>
+    <t>Meir Linzen</t>
+  </si>
+  <si>
+    <t>linzen@herzoglaw.co.il</t>
+  </si>
+  <si>
+    <t>972 3 692 2020</t>
+  </si>
+  <si>
+    <t>https://herzoglaw.co.il/en/our-team/meir-linzen/</t>
+  </si>
+  <si>
+    <t>Chairman</t>
+  </si>
+  <si>
+    <t>Gil White</t>
+  </si>
+  <si>
+    <t>whiteg@herzoglaw.co.il</t>
+  </si>
+  <si>
+    <t>e-commerce sector</t>
+  </si>
+  <si>
+    <t>https://herzoglaw.co.il/en/our-team/gil-white/</t>
+  </si>
+  <si>
+    <t>Samer Haj-Yehia</t>
+  </si>
+  <si>
+    <t>hajyehias@herzoglaw.co.il</t>
+  </si>
+  <si>
+    <t>corporate culture and governance</t>
+  </si>
+  <si>
+    <t>https://herzoglaw.co.il/en/our-team/samer-haj-yehia-dr/</t>
+  </si>
+  <si>
+    <t>Amir Seraya</t>
+  </si>
+  <si>
+    <t>seraya@herzoglaw.co.il</t>
+  </si>
+  <si>
+    <t>https://herzoglaw.co.il/en/our-team/amir-seraya/</t>
+  </si>
+  <si>
+    <t>Alan Sacks</t>
+  </si>
+  <si>
+    <t>sacksa@herzoglaw.co.il</t>
+  </si>
+  <si>
+    <t>https://herzoglaw.co.il/en/our-team/alan-sacks/</t>
+  </si>
+  <si>
+    <t>Tania Boulanger</t>
+  </si>
+  <si>
+    <t>tania.boulanger@mcmillan.ca</t>
+  </si>
+  <si>
+    <t>tel:514.375.5100</t>
+  </si>
+  <si>
+    <t>Capital Markets &amp; Securities</t>
+  </si>
+  <si>
+    <t>https://mcmillan.ca/people/tania-boulanger/</t>
+  </si>
+  <si>
+    <t>Mc Millan</t>
+  </si>
+  <si>
+    <t>Gillian Eliahoo</t>
+  </si>
+  <si>
+    <t>gillian.eliahoo@mcmillan.ca</t>
+  </si>
+  <si>
+    <t>tel:647.943.8066</t>
+  </si>
+  <si>
+    <t>https://mcmillan.ca/people/gillian-eliahoo/</t>
+  </si>
+  <si>
+    <t>Robin M. Junger</t>
+  </si>
+  <si>
+    <t>robin.junger@mcmillan.ca</t>
+  </si>
+  <si>
+    <t>tel:778.329.7523 | 403.531.4711</t>
+  </si>
+  <si>
+    <t>Indigenous Law</t>
+  </si>
+  <si>
+    <t>https://mcmillan.ca/people/robin-junger/</t>
+  </si>
+  <si>
+    <t>Jonathan Kalles</t>
+  </si>
+  <si>
+    <t>jonathan.kalles@mcmillan.ca</t>
+  </si>
+  <si>
+    <t>tel:514.375.5146</t>
+  </si>
+  <si>
+    <t>Government &amp; Public Policy</t>
+  </si>
+  <si>
+    <t>https://mcmillan.ca/people/jonathan-kalles/</t>
+  </si>
+  <si>
+    <t>Maxime Lemieux</t>
+  </si>
+  <si>
+    <t>maxime.lemieux@mcmillan.ca</t>
+  </si>
+  <si>
+    <t>tel:514.375.5172</t>
+  </si>
+  <si>
+    <t>https://mcmillan.ca/people/maxime-lemieux/</t>
+  </si>
+  <si>
+    <t>Litigation,</t>
+  </si>
+  <si>
+    <t>Itay Brafman</t>
+  </si>
+  <si>
+    <t>ibrafman@fbclawyers.com</t>
+  </si>
+  <si>
+    <t>https://www.fbclawyers.com/lawyer/itay-brafman/</t>
+  </si>
+  <si>
+    <t>Itay Zemel</t>
+  </si>
+  <si>
+    <t>izemel@fbclawyers.com</t>
+  </si>
+  <si>
+    <t>972.3.694.4190</t>
+  </si>
+  <si>
+    <t>https://www.fbclawyers.com/lawyer/itay-zemel-2/</t>
+  </si>
+  <si>
+    <t>Itiel Ben-Haim</t>
+  </si>
+  <si>
+    <t>iben@fbclawyers.com</t>
+  </si>
+  <si>
+    <t>972.3.694.4194</t>
+  </si>
+  <si>
+    <t>https://www.fbclawyers.com/lawyer/itiel-ben-haim/</t>
+  </si>
+  <si>
+    <t>Jana Rabinovich</t>
+  </si>
+  <si>
+    <t>jrabinovich@fbclawyers.com</t>
+  </si>
+  <si>
+    <t>https://www.fbclawyers.com/lawyer/jana-rabinovich/</t>
+  </si>
+  <si>
+    <t>Helena Dalton</t>
+  </si>
+  <si>
+    <t>helena.dalton@arthurcox.com</t>
+  </si>
+  <si>
+    <t>tel:+353 1 920 2357</t>
+  </si>
+  <si>
+    <t>financial services industry</t>
+  </si>
+  <si>
+    <t>https://www.arthurcox.com/people/helena-dalton/</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>Emma Hickey</t>
+  </si>
+  <si>
+    <t>emma.hickey@arthurcox.com</t>
+  </si>
+  <si>
+    <t>tel:+353 1 920 1179</t>
+  </si>
+  <si>
+    <t>https://www.arthurcox.com/people/emma-hickey/</t>
+  </si>
+  <si>
+    <t>Karen Leonard</t>
+  </si>
+  <si>
+    <t>karen.leonard@arthurcox.com</t>
+  </si>
+  <si>
+    <t>tel:+353 1 920 1237</t>
+  </si>
+  <si>
+    <t>corporate governance</t>
+  </si>
+  <si>
+    <t>https://www.arthurcox.com/people/karen-leonard/</t>
+  </si>
+  <si>
+    <t>Seán O’Flaherty</t>
+  </si>
+  <si>
+    <t>sean.oflaherty@arthurcox.com</t>
+  </si>
+  <si>
+    <t>tel:+353 1 920 1399</t>
+  </si>
+  <si>
+    <t>https://www.arthurcox.com/people/sean-oflaherty/</t>
+  </si>
+  <si>
+    <t>Pamela Sullivan</t>
+  </si>
+  <si>
+    <t>Pamela.Sullivan@arthurcox.com</t>
+  </si>
+  <si>
+    <t>tel:+353 1 920 1445</t>
+  </si>
+  <si>
+    <t>Governance</t>
+  </si>
+  <si>
+    <t>https://www.arthurcox.com/people/pamela-sullivan/</t>
+  </si>
+  <si>
+    <t>502 2324 3939</t>
+  </si>
+  <si>
+    <t>GUATEMALA</t>
+  </si>
+  <si>
+    <t>SENIOR ASSOCIATE</t>
+  </si>
+  <si>
+    <t>Consortium Legal</t>
+  </si>
+  <si>
+    <t>Alexandra Adams</t>
+  </si>
+  <si>
+    <t>alexandra.adams@maddocks.com.au</t>
+  </si>
+  <si>
+    <t>tel:+61 2 9291 6117</t>
+  </si>
+  <si>
+    <t>commercial and regulatory</t>
+  </si>
+  <si>
+    <t>https://www.maddocks.com.au/our-people/alexandra-adams</t>
+  </si>
+  <si>
+    <t>Georgia Andrianakos</t>
+  </si>
+  <si>
+    <t>georgia.andrianakos@maddocks.com.au</t>
+  </si>
+  <si>
+    <t>tel:+61 3 9258 3308</t>
+  </si>
+  <si>
+    <t>estate litigation</t>
+  </si>
+  <si>
+    <t>https://www.maddocks.com.au/our-people/georgia-andrianakos</t>
+  </si>
+  <si>
+    <t>Georgia Appleby</t>
+  </si>
+  <si>
+    <t>georgia.appleby@maddocks.com.au</t>
+  </si>
+  <si>
+    <t>tel:+61 2 9291 6059</t>
+  </si>
+  <si>
+    <t>planning and environmental law</t>
+  </si>
+  <si>
+    <t>https://www.maddocks.com.au/our-people/georgia-appleby</t>
+  </si>
+  <si>
+    <t>Michael McDonald</t>
+  </si>
+  <si>
+    <t>michael.mcdonald@maddocks.com.au</t>
+  </si>
+  <si>
+    <t>tel:+61 3 9258 3859</t>
+  </si>
+  <si>
+    <t>property acquisitions and disposals</t>
+  </si>
+  <si>
+    <t>https://www.maddocks.com.au/our-people/michael-mcdonald</t>
+  </si>
+  <si>
+    <t>Shane Ridley</t>
+  </si>
+  <si>
+    <t>shane.ridley@maddocks.com.au</t>
+  </si>
+  <si>
+    <t>tel:+61 3 9258 3519</t>
+  </si>
+  <si>
+    <t>consortiums on construction</t>
+  </si>
+  <si>
+    <t>https://www.maddocks.com.au/our-people/shane-ridley</t>
+  </si>
+  <si>
+    <t>Tel. +44 (0)20 7925 2244</t>
+  </si>
+  <si>
+    <t>appraising legal, financial and reputational risk</t>
+  </si>
+  <si>
+    <t>Tel. 0044 (0) 20 7004 2660</t>
+  </si>
+  <si>
+    <t>Jaffar Rakhimov</t>
+  </si>
+  <si>
+    <t>jaffar.rakhimov@belluzzo.net</t>
+  </si>
+  <si>
+    <t>family office institutions</t>
+  </si>
+  <si>
+    <t>https://belluzzo.net/en/professionals/jaffar-rakhimov</t>
+  </si>
+  <si>
+    <t>Tel. 0039 02 365 69657</t>
+  </si>
+  <si>
+    <t>Tax Law</t>
+  </si>
+  <si>
+    <t>Financial Services sector</t>
+  </si>
+  <si>
+    <t>DWF Group</t>
+  </si>
+  <si>
+    <t>abigail.jennings@dwf.law</t>
+  </si>
+  <si>
+    <t>Adolf Rousaud</t>
+  </si>
+  <si>
+    <t>adolf.rousaud@dwf-rcd.law</t>
+  </si>
+  <si>
+    <t>tel:+34917583906+34935034868</t>
+  </si>
+  <si>
+    <t>Corporate and Commercial matters</t>
+  </si>
+  <si>
+    <t>https://dwfgroup.com/en/people/a/adolf-rousaud</t>
+  </si>
+  <si>
+    <t>Global Head of Corporate</t>
+  </si>
+  <si>
+    <t>Catastrophic Injury &amp; Occupational Health</t>
+  </si>
+  <si>
+    <t>Agnieszka Chylińska</t>
+  </si>
+  <si>
+    <t>agnieszka.chylinska@dwf.law</t>
+  </si>
+  <si>
+    <t>tel:+48226534316</t>
+  </si>
+  <si>
+    <t>complex infrastructure projects</t>
+  </si>
+  <si>
+    <t>https://dwfgroup.com/en/people/a/agnieszka-chylinska</t>
+  </si>
+  <si>
+    <t>cybersecurity, IT compliance</t>
+  </si>
+  <si>
+    <t>Cecilia Amieva</t>
+  </si>
+  <si>
+    <t>camieva@ecija.com</t>
+  </si>
+  <si>
+    <t>tel:+598 99 455 958</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>corporate sustainability</t>
+  </si>
+  <si>
+    <t>https://www.ecija.com/en/lawyers/cecilia-amieva/</t>
+  </si>
+  <si>
+    <t>Managing Parner</t>
+  </si>
+  <si>
+    <t>Alberto Sanjuán</t>
+  </si>
+  <si>
+    <t>asanjuan@ecija.com</t>
+  </si>
+  <si>
+    <t>tel:+34 97 637 17 16</t>
+  </si>
+  <si>
+    <t>restructuring, litigation</t>
+  </si>
+  <si>
+    <t>https://www.ecija.com/en/lawyers/alberto-sanjuan/</t>
+  </si>
+  <si>
+    <t>Managing partner</t>
+  </si>
+  <si>
+    <t>Alfredo Moreno</t>
+  </si>
+  <si>
+    <t>amoreno@ecija.com</t>
+  </si>
+  <si>
+    <t>tel:(562) 23618900</t>
+  </si>
+  <si>
+    <t>commercial law, M&amp;A</t>
+  </si>
+  <si>
+    <t>https://www.ecija.com/en/lawyers/alfredo-moreno/</t>
+  </si>
+  <si>
+    <t>Dan Morton</t>
+  </si>
+  <si>
+    <t>Dan.Morton@jmw.co.uk</t>
+  </si>
+  <si>
+    <t>technology</t>
+  </si>
+  <si>
+    <t>https://www.jmw.co.uk/people/dan-morton</t>
+  </si>
+  <si>
+    <t>IT Director</t>
+  </si>
+  <si>
+    <t>Paul Coombes</t>
+  </si>
+  <si>
+    <t>Paul.Coombes@jmw.co.uk</t>
+  </si>
+  <si>
+    <t>Lawshare</t>
+  </si>
+  <si>
+    <t>https://www.jmw.co.uk/people/paul-coombes</t>
+  </si>
+  <si>
+    <t>Danielle Carter</t>
+  </si>
+  <si>
+    <t>danielle.carter@jmw.co.uk</t>
+  </si>
+  <si>
+    <t>tel:+443300292025</t>
+  </si>
+  <si>
+    <t>Finance and Operations</t>
+  </si>
+  <si>
+    <t>https://www.jmw.co.uk/people/danielle-carter</t>
+  </si>
+  <si>
+    <t>COP Operations &amp; Finance Partner</t>
+  </si>
+  <si>
+    <t>Stuart Cartwright</t>
+  </si>
+  <si>
+    <t>Stuart.Cartwright@jmw.co.uk</t>
+  </si>
+  <si>
+    <t>https://www.jmw.co.uk/people/stuart-cartwright</t>
+  </si>
+  <si>
+    <t>Head of Business Development</t>
+  </si>
+  <si>
+    <t>Chris Sutton</t>
+  </si>
+  <si>
+    <t>Chris.Sutton@jmw.co.uk</t>
+  </si>
+  <si>
+    <t>https://www.jmw.co.uk/people/chris-sutton</t>
+  </si>
+  <si>
+    <t>tel:+44 20 7667 9425</t>
+  </si>
+  <si>
+    <t>Financial institutions</t>
+  </si>
+  <si>
+    <t>tel:+44 20 7667 9116</t>
+  </si>
+  <si>
+    <t>Commercial, IT and outsourcing</t>
+  </si>
+  <si>
+    <t>Adam McGahan</t>
+  </si>
+  <si>
+    <t>Adam.McGahan@kennedyslaw.com</t>
+  </si>
+  <si>
+    <t>tel:+44 28 9026 1475</t>
+  </si>
+  <si>
+    <t>Employers' liability</t>
+  </si>
+  <si>
+    <t>https://www.kennedyslaw.com/en/our-people/people/belfast/adam-mcgahan/</t>
+  </si>
+  <si>
+    <t>Adam Osieke</t>
+  </si>
+  <si>
+    <t>Adam.Osieke@kennedyslaw.com</t>
+  </si>
+  <si>
+    <t>tel:+44 20 7667 9343</t>
+  </si>
+  <si>
+    <t>Property damage</t>
+  </si>
+  <si>
+    <t>https://www.kennedyslaw.com/en/our-people/people/london/adam-osieke/</t>
+  </si>
+  <si>
+    <t>Legal Director</t>
+  </si>
+  <si>
+    <t>Ailbhe Kirrane</t>
+  </si>
+  <si>
+    <t>Ailbhe.Kirrane@kennedyslaw.com</t>
+  </si>
+  <si>
+    <t>tel:+61 3 9498 6667</t>
+  </si>
+  <si>
+    <t>Directors and officers liability</t>
+  </si>
+  <si>
+    <t>https://www.kennedyslaw.com/en/our-people/people/melbourne/ailbhe-kirrane/</t>
+  </si>
+  <si>
+    <t>Aishling Walsh</t>
+  </si>
+  <si>
+    <t>Aishling.Walsh@kennedyslaw.com</t>
+  </si>
+  <si>
+    <t>tel:+353 1 482 5710</t>
+  </si>
+  <si>
+    <t>Product liability and product safety</t>
+  </si>
+  <si>
+    <t>https://www.kennedyslaw.com/en/our-people/people/dublin/aishling-walsh/</t>
+  </si>
+  <si>
+    <t>tax disputes</t>
+  </si>
+  <si>
+    <t>MacFarlanes</t>
+  </si>
+  <si>
+    <t>PFI project companies</t>
+  </si>
+  <si>
+    <t>harriet.miller@macfarlanes.com,</t>
+  </si>
+  <si>
+    <t>commercially competitive and aligned</t>
+  </si>
+  <si>
+    <t>private capital fund transactions</t>
+  </si>
+  <si>
+    <t>cross-border</t>
+  </si>
+  <si>
+    <t>oil and gas sector</t>
+  </si>
+  <si>
+    <t>Marks &amp; Clerk</t>
+  </si>
+  <si>
+    <t>technical subject matter</t>
+  </si>
+  <si>
+    <t>Office Managing Partner</t>
+  </si>
+  <si>
+    <t>Catherine Lovrics</t>
+  </si>
+  <si>
+    <t>clovrics@marks-clerk.ca</t>
+  </si>
+  <si>
+    <t>tel:+14165951155</t>
+  </si>
+  <si>
+    <t>trademarks, copyrights</t>
+  </si>
+  <si>
+    <t>https://www.marks-clerk.com/our-people/catherine-lovrics/</t>
+  </si>
+  <si>
+    <t>Claire Keating</t>
+  </si>
+  <si>
+    <t>ckeating@marks-clerk.com</t>
+  </si>
+  <si>
+    <t>tel:+441223345520</t>
+  </si>
+  <si>
+    <t>Brands &amp; Trade Marks</t>
+  </si>
+  <si>
+    <t>https://www.marks-clerk.com/our-people/claire-keating/</t>
+  </si>
+  <si>
+    <t>tel:+86-10-5965-2986</t>
+  </si>
+  <si>
+    <t>mergers and acquisitions and private equity</t>
+  </si>
+  <si>
+    <t>STB Law</t>
+  </si>
+  <si>
+    <t>tel:+86-10-5965-2976</t>
+  </si>
+  <si>
+    <t>Alternative Dispute Resolution</t>
+  </si>
+  <si>
+    <t>senior counsel</t>
+  </si>
+  <si>
+    <t>Greens List</t>
+  </si>
+  <si>
+    <t>Geoffrey Nettle</t>
+  </si>
+  <si>
+    <t>arbitration and investigations</t>
+  </si>
+  <si>
+    <t>AC KC</t>
+  </si>
+  <si>
+    <t>Andrew Woods</t>
+  </si>
+  <si>
+    <t>andrew.woods@vicbar.com.au</t>
+  </si>
+  <si>
+    <t>61 3 9225 6649</t>
+  </si>
+  <si>
+    <t>commercial, regulatory crime</t>
+  </si>
+  <si>
+    <t>https://www.greenslist.com.au/s/barrister/00330000010bddwAAA/andrew-woods-sc</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>Carolyn Symons</t>
+  </si>
+  <si>
+    <t>symons@vicbar.com.au</t>
+  </si>
+  <si>
+    <t>61 3 9225 6378</t>
+  </si>
+  <si>
+    <t>personal and corporate insolvency and insurance</t>
+  </si>
+  <si>
+    <t>https://www.greenslist.com.au/s/barrister/003a000001Vdub0AAB/carolyn-symons</t>
+  </si>
+  <si>
+    <t>Peter Caillard</t>
+  </si>
+  <si>
+    <t>pcaillard@vicbar.com.au</t>
+  </si>
+  <si>
+    <t>commercial</t>
+  </si>
+  <si>
+    <t>https://www.greenslist.com.au/s/barrister/00330000012D1q6AAC/peter-caillard</t>
+  </si>
+  <si>
+    <t>Alexander Millman</t>
+  </si>
+  <si>
+    <t>amillman@millsoakley.com.au</t>
+  </si>
+  <si>
+    <t>61 499 220 541</t>
+  </si>
+  <si>
+    <t>Workplace Relations</t>
+  </si>
+  <si>
+    <t>https://www.millsoakley.com.au/our-people/alexander-millman/</t>
+  </si>
+  <si>
+    <t>family law</t>
+  </si>
+  <si>
+    <t>Alexandra Streltsova</t>
+  </si>
+  <si>
+    <t>astreltsova@millsoakley.com.au</t>
+  </si>
+  <si>
+    <t>61 427 456 576</t>
+  </si>
+  <si>
+    <t>https://www.millsoakley.com.au/our-people/alexandra-streltsova/</t>
+  </si>
+  <si>
+    <t>Alison Malek</t>
+  </si>
+  <si>
+    <t>amalek@millsoakley.com.au</t>
+  </si>
+  <si>
+    <t>61 411 482 219</t>
+  </si>
+  <si>
+    <t>https://www.millsoakley.com.au/our-people/alison-malek/</t>
+  </si>
+  <si>
+    <t>Alissa Harnath</t>
+  </si>
+  <si>
+    <t>aharnath@millsoakley.com.au</t>
+  </si>
+  <si>
+    <t>61 3 9605 0012</t>
+  </si>
+  <si>
+    <t>https://www.millsoakley.com.au/our-people/alissa-harnath/</t>
+  </si>
+  <si>
+    <t>PETER NGAI</t>
+  </si>
+  <si>
+    <t>PN@pcwoo.com.hk</t>
+  </si>
+  <si>
+    <t>(852) 2523-1825</t>
+  </si>
+  <si>
+    <t>https://www.pcwoo.com.hk/en/people/detail/29/?back=8e3ee9833ee21f43bbbd8ae41b0cfcee</t>
+  </si>
+  <si>
+    <t>EMILY LAM</t>
+  </si>
+  <si>
+    <t>EL@pcwoo.com.hk</t>
+  </si>
+  <si>
+    <t>(852) 2533-7607</t>
+  </si>
+  <si>
+    <t>https://www.pcwoo.com.hk/en/people/detail/4/?back=8e3ee9833ee21f43bbbd8ae41b0cfcee</t>
+  </si>
+  <si>
+    <t>https://www.pcwoo.com.hk/en/people/detail/35/?back=8e3ee9833ee21f43bbbd8ae41b0cfcee</t>
+  </si>
+  <si>
+    <t>https://www.pcwoo.com.hk/en/people/detail/36/?back=8e3ee9833ee21f43bbbd8ae41b0cfcee</t>
+  </si>
+  <si>
+    <t>https://www.pcwoo.com.hk/en/people/detail/38/?back=8e3ee9833ee21f43bbbd8ae41b0cfcee</t>
+  </si>
+  <si>
+    <t>private equity, strategic mergers &amp; acquisitions</t>
+  </si>
+  <si>
+    <t>Alexandra Flaus</t>
+  </si>
+  <si>
+    <t>alexandra.flaus@webbhenderson.com</t>
+  </si>
+  <si>
+    <t>tel:+64 27 309 0321</t>
+  </si>
+  <si>
+    <t>https://webbhenderson.com/people/alexandra-flaus/</t>
+  </si>
+  <si>
+    <t>Annaliese McIntyre</t>
+  </si>
+  <si>
+    <t>annaliese.mcintyre@webbhenderson.com</t>
+  </si>
+  <si>
+    <t>tel:+64 21 034 0212</t>
+  </si>
+  <si>
+    <t>https://webbhenderson.com/people/annaliese-mcintyre/</t>
+  </si>
+  <si>
+    <t>Ben Coffey</t>
+  </si>
+  <si>
+    <t>ben.coffey@webbhenderson.com</t>
+  </si>
+  <si>
+    <t>tel:+64 27 700 9376</t>
+  </si>
+  <si>
+    <t>https://webbhenderson.com/people/ben-coffey/</t>
+  </si>
+  <si>
+    <t>Bhumika Khatri</t>
+  </si>
+  <si>
+    <t>bhumika.khatri@webbhenderson.com</t>
+  </si>
+  <si>
+    <t>tel:+61 408 039 261</t>
+  </si>
+  <si>
+    <t>https://webbhenderson.com/people/bhumika-khatri/</t>
+  </si>
+  <si>
+    <t>Henry Lynch</t>
+  </si>
+  <si>
+    <t>henry.lynch@webbhenderson.com</t>
+  </si>
+  <si>
+    <t>tel:+61 2 8214 3500</t>
+  </si>
+  <si>
+    <t>https://webbhenderson.com/people/henry-lynch/</t>
+  </si>
+  <si>
+    <t>insurance and personal injury litigation</t>
+  </si>
+  <si>
+    <t>Arbitration and investigations</t>
+  </si>
+  <si>
+    <t>Corporate Finance/ Company</t>
+  </si>
+  <si>
+    <t>Nanette Botes</t>
+  </si>
+  <si>
+    <t>nbotes@kcauditsupport.nl</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Corporate Legal Services</t>
+  </si>
+  <si>
+    <t>https://kcalliance.nl/people/?_title=senior-manager</t>
+  </si>
+  <si>
+    <t>Senior Auditor</t>
+  </si>
+  <si>
+    <t>Theanette Brits</t>
+  </si>
+  <si>
+    <t>tbrits@kcauditsupport.nl</t>
+  </si>
+  <si>
+    <t>Tax Reporting</t>
+  </si>
+  <si>
+    <t>Audit Supervisor</t>
+  </si>
+  <si>
+    <t>Pieter Crous</t>
+  </si>
+  <si>
+    <t>pcrous@kcauditsupport.nl</t>
+  </si>
+  <si>
+    <t>VAT Fiscal </t>
+  </si>
+  <si>
+    <t>Senior Audit Manager</t>
+  </si>
+  <si>
+    <t>Cecilson Grazette</t>
+  </si>
+  <si>
+    <t>cgrazette@kclegal.nl</t>
+  </si>
+  <si>
+    <t>Wage Tax</t>
+  </si>
+  <si>
+    <t>Senior Manager Tax</t>
   </si>
   <si>
     <t>Litigation </t>
@@ -16446,7 +17649,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="E1:N1347"/>
+  <dimension ref="E1:N1475"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="6" max="6" width="38.25" customWidth="1"/>
@@ -49081,6 +50284,3224 @@
       </c>
       <c r="N1347" s="2" t="s">
         <v>5066</v>
+      </c>
+    </row>
+    <row r="1349" spans="5:14">
+      <c r="E1349" t="s">
+        <v>5072</v>
+      </c>
+      <c r="F1349" t="s">
+        <v>5073</v>
+      </c>
+      <c r="G1349" t="s">
+        <v>5074</v>
+      </c>
+      <c r="H1349" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1349" t="s">
+        <v>1166</v>
+      </c>
+      <c r="J1349" t="s">
+        <v>5075</v>
+      </c>
+      <c r="M1349" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1349" s="2" t="s">
+        <v>4699</v>
+      </c>
+    </row>
+    <row r="1350" spans="5:14">
+      <c r="E1350" t="s">
+        <v>5077</v>
+      </c>
+      <c r="F1350" t="s">
+        <v>5078</v>
+      </c>
+      <c r="G1350" t="s">
+        <v>4702</v>
+      </c>
+      <c r="H1350" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1350" t="s">
+        <v>5079</v>
+      </c>
+      <c r="J1350" t="s">
+        <v>5080</v>
+      </c>
+      <c r="M1350" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1350" s="2" t="s">
+        <v>4699</v>
+      </c>
+    </row>
+    <row r="1351" spans="5:14">
+      <c r="E1351" t="s">
+        <v>5081</v>
+      </c>
+      <c r="F1351" t="s">
+        <v>5082</v>
+      </c>
+      <c r="G1351" t="s">
+        <v>4702</v>
+      </c>
+      <c r="H1351" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1351" t="s">
+        <v>5083</v>
+      </c>
+      <c r="J1351" t="s">
+        <v>5084</v>
+      </c>
+      <c r="M1351" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1351" s="2" t="s">
+        <v>4699</v>
+      </c>
+    </row>
+    <row r="1352" spans="5:14">
+      <c r="E1352" t="s">
+        <v>5085</v>
+      </c>
+      <c r="F1352" t="s">
+        <v>5086</v>
+      </c>
+      <c r="G1352" t="s">
+        <v>5087</v>
+      </c>
+      <c r="H1352" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1352" t="s">
+        <v>5088</v>
+      </c>
+      <c r="J1352" t="s">
+        <v>5089</v>
+      </c>
+      <c r="M1352" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1352" s="2" t="s">
+        <v>4699</v>
+      </c>
+    </row>
+    <row r="1353" spans="5:14">
+      <c r="E1353" t="s">
+        <v>5090</v>
+      </c>
+      <c r="F1353" t="s">
+        <v>5091</v>
+      </c>
+      <c r="G1353" t="s">
+        <v>4702</v>
+      </c>
+      <c r="H1353" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1353" t="s">
+        <v>219</v>
+      </c>
+      <c r="J1353" t="s">
+        <v>5092</v>
+      </c>
+      <c r="M1353" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1353" s="2" t="s">
+        <v>4699</v>
+      </c>
+    </row>
+    <row r="1354" spans="5:14">
+      <c r="E1354" t="s">
+        <v>5093</v>
+      </c>
+      <c r="F1354" t="s">
+        <v>5094</v>
+      </c>
+      <c r="H1354" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1354" t="s">
+        <v>5095</v>
+      </c>
+      <c r="J1354" t="s">
+        <v>5096</v>
+      </c>
+      <c r="M1354" t="s">
+        <v>111</v>
+      </c>
+      <c r="N1354" s="2" t="s">
+        <v>5097</v>
+      </c>
+    </row>
+    <row r="1355" spans="5:14">
+      <c r="E1355" t="s">
+        <v>5098</v>
+      </c>
+      <c r="F1355" t="s">
+        <v>5099</v>
+      </c>
+      <c r="G1355" t="s">
+        <v>5100</v>
+      </c>
+      <c r="H1355" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1355" t="s">
+        <v>5101</v>
+      </c>
+      <c r="J1355" t="s">
+        <v>5102</v>
+      </c>
+      <c r="M1355" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1355" s="2" t="s">
+        <v>5097</v>
+      </c>
+    </row>
+    <row r="1356" spans="5:14">
+      <c r="E1356" t="s">
+        <v>5103</v>
+      </c>
+      <c r="F1356" t="s">
+        <v>5104</v>
+      </c>
+      <c r="G1356" t="s">
+        <v>5105</v>
+      </c>
+      <c r="H1356" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="I1356" t="s">
+        <v>5106</v>
+      </c>
+      <c r="J1356" t="s">
+        <v>5107</v>
+      </c>
+      <c r="M1356" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1356" s="2" t="s">
+        <v>5097</v>
+      </c>
+    </row>
+    <row r="1357" spans="5:14">
+      <c r="E1357" t="s">
+        <v>5108</v>
+      </c>
+      <c r="F1357" t="s">
+        <v>5109</v>
+      </c>
+      <c r="G1357" t="s">
+        <v>5110</v>
+      </c>
+      <c r="H1357" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="I1357" t="s">
+        <v>568</v>
+      </c>
+      <c r="J1357" t="s">
+        <v>5111</v>
+      </c>
+      <c r="M1357" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1357" s="2" t="s">
+        <v>5097</v>
+      </c>
+    </row>
+    <row r="1358" spans="5:14">
+      <c r="E1358" t="s">
+        <v>5112</v>
+      </c>
+      <c r="F1358" t="s">
+        <v>5113</v>
+      </c>
+      <c r="H1358" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="I1358" t="s">
+        <v>5114</v>
+      </c>
+      <c r="J1358" t="s">
+        <v>5115</v>
+      </c>
+      <c r="M1358" t="s">
+        <v>5116</v>
+      </c>
+      <c r="N1358" s="2" t="s">
+        <v>5097</v>
+      </c>
+    </row>
+    <row r="1359" spans="5:14">
+      <c r="E1359" t="s">
+        <v>5117</v>
+      </c>
+      <c r="F1359" t="s">
+        <v>4132</v>
+      </c>
+      <c r="G1359" t="s">
+        <v>4133</v>
+      </c>
+      <c r="H1359" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1359" t="s">
+        <v>5118</v>
+      </c>
+      <c r="J1359" t="s">
+        <v>5119</v>
+      </c>
+      <c r="M1359" t="s">
+        <v>975</v>
+      </c>
+      <c r="N1359" s="2" t="s">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="1360" spans="5:14">
+      <c r="E1360" t="s">
+        <v>4137</v>
+      </c>
+      <c r="F1360" t="s">
+        <v>4138</v>
+      </c>
+      <c r="G1360" t="s">
+        <v>4133</v>
+      </c>
+      <c r="H1360" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1360" t="s">
+        <v>5121</v>
+      </c>
+      <c r="J1360" t="s">
+        <v>4139</v>
+      </c>
+      <c r="M1360" t="s">
+        <v>975</v>
+      </c>
+      <c r="N1360" s="2" t="s">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="1361" spans="5:14">
+      <c r="E1361" t="s">
+        <v>4131</v>
+      </c>
+      <c r="F1361" t="s">
+        <v>4132</v>
+      </c>
+      <c r="G1361" t="s">
+        <v>4133</v>
+      </c>
+      <c r="H1361" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1361" t="s">
+        <v>4134</v>
+      </c>
+      <c r="J1361" t="s">
+        <v>4135</v>
+      </c>
+      <c r="M1361" t="s">
+        <v>975</v>
+      </c>
+      <c r="N1361" s="2" t="s">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="1362" spans="5:14">
+      <c r="E1362" t="s">
+        <v>5122</v>
+      </c>
+      <c r="F1362" t="s">
+        <v>5123</v>
+      </c>
+      <c r="G1362" t="s">
+        <v>5124</v>
+      </c>
+      <c r="H1362" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1362" t="s">
+        <v>1479</v>
+      </c>
+      <c r="J1362" t="s">
+        <v>5125</v>
+      </c>
+      <c r="M1362" t="s">
+        <v>111</v>
+      </c>
+      <c r="N1362" s="2" t="s">
+        <v>5126</v>
+      </c>
+    </row>
+    <row r="1363" spans="5:14">
+      <c r="E1363" t="s">
+        <v>5127</v>
+      </c>
+      <c r="F1363" t="s">
+        <v>5128</v>
+      </c>
+      <c r="G1363" t="s">
+        <v>5129</v>
+      </c>
+      <c r="H1363" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1363" t="s">
+        <v>3282</v>
+      </c>
+      <c r="J1363" t="s">
+        <v>5130</v>
+      </c>
+      <c r="M1363" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1363" s="2" t="s">
+        <v>5126</v>
+      </c>
+    </row>
+    <row r="1364" spans="5:14">
+      <c r="E1364" t="s">
+        <v>5131</v>
+      </c>
+      <c r="F1364" t="s">
+        <v>5132</v>
+      </c>
+      <c r="G1364" t="s">
+        <v>5133</v>
+      </c>
+      <c r="H1364" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1364" t="s">
+        <v>219</v>
+      </c>
+      <c r="J1364" t="s">
+        <v>5134</v>
+      </c>
+      <c r="M1364" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1364" s="2" t="s">
+        <v>5126</v>
+      </c>
+    </row>
+    <row r="1365" spans="5:14">
+      <c r="E1365" t="s">
+        <v>5135</v>
+      </c>
+      <c r="F1365" t="s">
+        <v>5136</v>
+      </c>
+      <c r="G1365" t="s">
+        <v>5137</v>
+      </c>
+      <c r="H1365" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1365" t="s">
+        <v>1350</v>
+      </c>
+      <c r="J1365" t="s">
+        <v>5138</v>
+      </c>
+      <c r="M1365" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1365" s="2" t="s">
+        <v>5126</v>
+      </c>
+    </row>
+    <row r="1366" spans="5:14">
+      <c r="E1366" t="s">
+        <v>5139</v>
+      </c>
+      <c r="F1366" t="s">
+        <v>5140</v>
+      </c>
+      <c r="G1366" t="s">
+        <v>5141</v>
+      </c>
+      <c r="H1366" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1366" t="s">
+        <v>408</v>
+      </c>
+      <c r="J1366" t="s">
+        <v>5142</v>
+      </c>
+      <c r="M1366" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1366" s="2" t="s">
+        <v>5126</v>
+      </c>
+    </row>
+    <row r="1367" spans="5:14">
+      <c r="E1367" t="s">
+        <v>5143</v>
+      </c>
+      <c r="F1367" t="s">
+        <v>5144</v>
+      </c>
+      <c r="G1367" t="s">
+        <v>5145</v>
+      </c>
+      <c r="H1367" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1367" t="s">
+        <v>5146</v>
+      </c>
+      <c r="J1367" t="s">
+        <v>5147</v>
+      </c>
+      <c r="M1367" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1367" s="2" t="s">
+        <v>5148</v>
+      </c>
+    </row>
+    <row r="1368" spans="5:14">
+      <c r="E1368" t="s">
+        <v>5149</v>
+      </c>
+      <c r="F1368" t="s">
+        <v>5150</v>
+      </c>
+      <c r="G1368" t="s">
+        <v>5151</v>
+      </c>
+      <c r="H1368" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1368" t="s">
+        <v>5152</v>
+      </c>
+      <c r="J1368" t="s">
+        <v>5153</v>
+      </c>
+      <c r="M1368" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1368" s="2" t="s">
+        <v>5154</v>
+      </c>
+    </row>
+    <row r="1369" spans="5:14">
+      <c r="E1369" t="s">
+        <v>5155</v>
+      </c>
+      <c r="F1369" t="s">
+        <v>5156</v>
+      </c>
+      <c r="G1369" t="s">
+        <v>5157</v>
+      </c>
+      <c r="H1369" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I1369" t="s">
+        <v>281</v>
+      </c>
+      <c r="J1369" t="s">
+        <v>5158</v>
+      </c>
+      <c r="M1369" t="s">
+        <v>5159</v>
+      </c>
+      <c r="N1369" s="2" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="1370" spans="5:14">
+      <c r="E1370" t="s">
+        <v>5160</v>
+      </c>
+      <c r="F1370" t="s">
+        <v>5161</v>
+      </c>
+      <c r="G1370" t="s">
+        <v>5157</v>
+      </c>
+      <c r="H1370" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I1370" t="s">
+        <v>5162</v>
+      </c>
+      <c r="J1370" t="s">
+        <v>5163</v>
+      </c>
+      <c r="M1370" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1370" s="2" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="1371" spans="5:14">
+      <c r="E1371" t="s">
+        <v>5164</v>
+      </c>
+      <c r="F1371" t="s">
+        <v>5165</v>
+      </c>
+      <c r="G1371" t="s">
+        <v>5157</v>
+      </c>
+      <c r="H1371" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I1371" t="s">
+        <v>5166</v>
+      </c>
+      <c r="J1371" t="s">
+        <v>5167</v>
+      </c>
+      <c r="M1371" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1371" s="2" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="1372" spans="5:14">
+      <c r="E1372" t="s">
+        <v>5168</v>
+      </c>
+      <c r="F1372" t="s">
+        <v>5169</v>
+      </c>
+      <c r="G1372" t="s">
+        <v>5157</v>
+      </c>
+      <c r="H1372" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I1372" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1372" t="s">
+        <v>5170</v>
+      </c>
+      <c r="M1372" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1372" s="2" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="1373" spans="5:14">
+      <c r="E1373" t="s">
+        <v>5171</v>
+      </c>
+      <c r="F1373" t="s">
+        <v>5172</v>
+      </c>
+      <c r="G1373" t="s">
+        <v>5157</v>
+      </c>
+      <c r="H1373" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I1373" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1373" t="s">
+        <v>5173</v>
+      </c>
+      <c r="M1373" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1373" s="2" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="1374" spans="5:14">
+      <c r="E1374" t="s">
+        <v>5174</v>
+      </c>
+      <c r="F1374" t="s">
+        <v>5175</v>
+      </c>
+      <c r="G1374" t="s">
+        <v>5176</v>
+      </c>
+      <c r="H1374" s="1" t="s">
+        <v>3387</v>
+      </c>
+      <c r="I1374" t="s">
+        <v>5177</v>
+      </c>
+      <c r="J1374" t="s">
+        <v>5178</v>
+      </c>
+      <c r="M1374" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1374" s="2" t="s">
+        <v>5179</v>
+      </c>
+    </row>
+    <row r="1375" spans="5:14">
+      <c r="E1375" t="s">
+        <v>5180</v>
+      </c>
+      <c r="F1375" t="s">
+        <v>5181</v>
+      </c>
+      <c r="G1375" t="s">
+        <v>5182</v>
+      </c>
+      <c r="H1375" s="1" t="s">
+        <v>3387</v>
+      </c>
+      <c r="I1375" t="s">
+        <v>4965</v>
+      </c>
+      <c r="J1375" t="s">
+        <v>5183</v>
+      </c>
+      <c r="M1375" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1375" s="2" t="s">
+        <v>5179</v>
+      </c>
+    </row>
+    <row r="1376" spans="5:14">
+      <c r="E1376" t="s">
+        <v>5184</v>
+      </c>
+      <c r="F1376" t="s">
+        <v>5185</v>
+      </c>
+      <c r="G1376" t="s">
+        <v>5186</v>
+      </c>
+      <c r="H1376" s="1" t="s">
+        <v>3387</v>
+      </c>
+      <c r="I1376" t="s">
+        <v>5187</v>
+      </c>
+      <c r="J1376" t="s">
+        <v>5188</v>
+      </c>
+      <c r="M1376" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1376" s="2" t="s">
+        <v>5179</v>
+      </c>
+    </row>
+    <row r="1377" spans="5:14">
+      <c r="E1377" t="s">
+        <v>5189</v>
+      </c>
+      <c r="F1377" t="s">
+        <v>5190</v>
+      </c>
+      <c r="G1377" t="s">
+        <v>5191</v>
+      </c>
+      <c r="H1377" s="1" t="s">
+        <v>3387</v>
+      </c>
+      <c r="I1377" t="s">
+        <v>5192</v>
+      </c>
+      <c r="J1377" t="s">
+        <v>5193</v>
+      </c>
+      <c r="M1377" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1377" s="2" t="s">
+        <v>5179</v>
+      </c>
+    </row>
+    <row r="1378" spans="5:14">
+      <c r="E1378" t="s">
+        <v>5194</v>
+      </c>
+      <c r="F1378" t="s">
+        <v>5195</v>
+      </c>
+      <c r="G1378" t="s">
+        <v>5196</v>
+      </c>
+      <c r="H1378" s="1" t="s">
+        <v>3387</v>
+      </c>
+      <c r="I1378" t="s">
+        <v>5177</v>
+      </c>
+      <c r="J1378" t="s">
+        <v>5197</v>
+      </c>
+      <c r="M1378" t="s">
+        <v>94</v>
+      </c>
+      <c r="N1378" s="2" t="s">
+        <v>5179</v>
+      </c>
+    </row>
+    <row r="1379" spans="5:14">
+      <c r="E1379" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F1379" t="s">
+        <v>2035</v>
+      </c>
+      <c r="G1379" t="s">
+        <v>1889</v>
+      </c>
+      <c r="H1379" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I1379" t="s">
+        <v>5198</v>
+      </c>
+      <c r="J1379" t="s">
+        <v>2037</v>
+      </c>
+      <c r="M1379" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1379" s="2" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="1380" spans="5:14">
+      <c r="E1380" t="s">
+        <v>5199</v>
+      </c>
+      <c r="F1380" t="s">
+        <v>5200</v>
+      </c>
+      <c r="G1380" t="s">
+        <v>2017</v>
+      </c>
+      <c r="H1380" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I1380" t="s">
+        <v>219</v>
+      </c>
+      <c r="J1380" t="s">
+        <v>5201</v>
+      </c>
+      <c r="M1380" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1380" s="2" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="1381" spans="5:14">
+      <c r="E1381" t="s">
+        <v>5202</v>
+      </c>
+      <c r="F1381" t="s">
+        <v>5203</v>
+      </c>
+      <c r="G1381" t="s">
+        <v>5204</v>
+      </c>
+      <c r="H1381" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I1381" t="s">
+        <v>404</v>
+      </c>
+      <c r="J1381" t="s">
+        <v>5205</v>
+      </c>
+      <c r="M1381" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1381" s="2" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="1382" spans="5:14">
+      <c r="E1382" t="s">
+        <v>5206</v>
+      </c>
+      <c r="F1382" t="s">
+        <v>5207</v>
+      </c>
+      <c r="G1382" t="s">
+        <v>5208</v>
+      </c>
+      <c r="H1382" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I1382" t="s">
+        <v>3967</v>
+      </c>
+      <c r="J1382" t="s">
+        <v>5209</v>
+      </c>
+      <c r="M1382" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1382" s="2" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="1383" spans="5:14">
+      <c r="E1383" t="s">
+        <v>5210</v>
+      </c>
+      <c r="F1383" t="s">
+        <v>5211</v>
+      </c>
+      <c r="G1383" t="s">
+        <v>1889</v>
+      </c>
+      <c r="H1383" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I1383" t="s">
+        <v>2036</v>
+      </c>
+      <c r="J1383" t="s">
+        <v>5212</v>
+      </c>
+      <c r="M1383" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1383" s="2" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="1384" spans="5:14">
+      <c r="E1384" t="s">
+        <v>5213</v>
+      </c>
+      <c r="F1384" t="s">
+        <v>5214</v>
+      </c>
+      <c r="G1384" t="s">
+        <v>5215</v>
+      </c>
+      <c r="H1384" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="I1384" t="s">
+        <v>5216</v>
+      </c>
+      <c r="J1384" t="s">
+        <v>5217</v>
+      </c>
+      <c r="M1384" t="s">
+        <v>599</v>
+      </c>
+      <c r="N1384" s="2" t="s">
+        <v>5218</v>
+      </c>
+    </row>
+    <row r="1385" spans="5:14">
+      <c r="E1385" t="s">
+        <v>5219</v>
+      </c>
+      <c r="F1385" t="s">
+        <v>5220</v>
+      </c>
+      <c r="G1385" t="s">
+        <v>5221</v>
+      </c>
+      <c r="H1385" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="I1385" t="s">
+        <v>5101</v>
+      </c>
+      <c r="J1385" t="s">
+        <v>5222</v>
+      </c>
+      <c r="M1385" t="s">
+        <v>599</v>
+      </c>
+      <c r="N1385" s="2" t="s">
+        <v>5218</v>
+      </c>
+    </row>
+    <row r="1386" spans="5:14">
+      <c r="E1386" t="s">
+        <v>5223</v>
+      </c>
+      <c r="F1386" t="s">
+        <v>5224</v>
+      </c>
+      <c r="G1386" t="s">
+        <v>5225</v>
+      </c>
+      <c r="H1386" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="I1386" t="s">
+        <v>5226</v>
+      </c>
+      <c r="J1386" t="s">
+        <v>5227</v>
+      </c>
+      <c r="M1386" t="s">
+        <v>599</v>
+      </c>
+      <c r="N1386" s="2" t="s">
+        <v>5218</v>
+      </c>
+    </row>
+    <row r="1387" spans="5:14">
+      <c r="E1387" t="s">
+        <v>5228</v>
+      </c>
+      <c r="F1387" t="s">
+        <v>5229</v>
+      </c>
+      <c r="G1387" t="s">
+        <v>5230</v>
+      </c>
+      <c r="H1387" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="I1387" t="s">
+        <v>5216</v>
+      </c>
+      <c r="J1387" t="s">
+        <v>5231</v>
+      </c>
+      <c r="M1387" t="s">
+        <v>599</v>
+      </c>
+      <c r="N1387" s="2" t="s">
+        <v>5218</v>
+      </c>
+    </row>
+    <row r="1388" spans="5:14">
+      <c r="E1388" t="s">
+        <v>5232</v>
+      </c>
+      <c r="F1388" t="s">
+        <v>5233</v>
+      </c>
+      <c r="G1388" t="s">
+        <v>5234</v>
+      </c>
+      <c r="H1388" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="I1388" t="s">
+        <v>5235</v>
+      </c>
+      <c r="J1388" t="s">
+        <v>5236</v>
+      </c>
+      <c r="M1388" t="s">
+        <v>599</v>
+      </c>
+      <c r="N1388" s="2" t="s">
+        <v>5218</v>
+      </c>
+    </row>
+    <row r="1389" spans="5:14">
+      <c r="E1389" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F1389" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G1389" t="s">
+        <v>5237</v>
+      </c>
+      <c r="H1389" s="1" t="s">
+        <v>5238</v>
+      </c>
+      <c r="I1389" t="s">
+        <v>1293</v>
+      </c>
+      <c r="J1389" t="s">
+        <v>1474</v>
+      </c>
+      <c r="M1389" t="s">
+        <v>5239</v>
+      </c>
+      <c r="N1389" s="2" t="s">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="1390" spans="5:14">
+      <c r="E1390" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F1390" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1390" t="s">
+        <v>5237</v>
+      </c>
+      <c r="H1390" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="I1390" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J1390" t="s">
+        <v>1488</v>
+      </c>
+      <c r="M1390" t="s">
+        <v>5239</v>
+      </c>
+      <c r="N1390" s="2" t="s">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="1391" spans="5:14">
+      <c r="E1391" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F1391" t="s">
+        <v>1466</v>
+      </c>
+      <c r="G1391" t="s">
+        <v>1467</v>
+      </c>
+      <c r="H1391" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="I1391" t="s">
+        <v>408</v>
+      </c>
+      <c r="J1391" t="s">
+        <v>1469</v>
+      </c>
+      <c r="M1391" t="s">
+        <v>5239</v>
+      </c>
+      <c r="N1391" s="2" t="s">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="1392" spans="5:14">
+      <c r="E1392" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F1392" t="s">
+        <v>1476</v>
+      </c>
+      <c r="G1392" t="s">
+        <v>1477</v>
+      </c>
+      <c r="H1392" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="I1392" t="s">
+        <v>1479</v>
+      </c>
+      <c r="J1392" t="s">
+        <v>1480</v>
+      </c>
+      <c r="M1392" t="s">
+        <v>5239</v>
+      </c>
+      <c r="N1392" s="2" t="s">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="1393" spans="5:14">
+      <c r="E1393" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F1393" t="s">
+        <v>1482</v>
+      </c>
+      <c r="G1393" t="s">
+        <v>1477</v>
+      </c>
+      <c r="H1393" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="I1393" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J1393" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M1393" t="s">
+        <v>5239</v>
+      </c>
+      <c r="N1393" s="2" t="s">
+        <v>5240</v>
+      </c>
+    </row>
+    <row r="1394" spans="5:14">
+      <c r="E1394" t="s">
+        <v>5241</v>
+      </c>
+      <c r="F1394" t="s">
+        <v>5242</v>
+      </c>
+      <c r="G1394" t="s">
+        <v>5243</v>
+      </c>
+      <c r="H1394" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1394" t="s">
+        <v>5244</v>
+      </c>
+      <c r="J1394" t="s">
+        <v>5245</v>
+      </c>
+      <c r="M1394" t="s">
+        <v>5239</v>
+      </c>
+      <c r="N1394" s="2" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="1395" spans="5:14">
+      <c r="E1395" t="s">
+        <v>5246</v>
+      </c>
+      <c r="F1395" t="s">
+        <v>5247</v>
+      </c>
+      <c r="G1395" t="s">
+        <v>5248</v>
+      </c>
+      <c r="H1395" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1395" t="s">
+        <v>5249</v>
+      </c>
+      <c r="J1395" t="s">
+        <v>5250</v>
+      </c>
+      <c r="M1395" t="s">
+        <v>5239</v>
+      </c>
+      <c r="N1395" s="2" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="1396" spans="5:14">
+      <c r="E1396" t="s">
+        <v>5251</v>
+      </c>
+      <c r="F1396" t="s">
+        <v>5252</v>
+      </c>
+      <c r="G1396" t="s">
+        <v>5253</v>
+      </c>
+      <c r="H1396" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1396" t="s">
+        <v>5254</v>
+      </c>
+      <c r="J1396" t="s">
+        <v>5255</v>
+      </c>
+      <c r="M1396" t="s">
+        <v>5239</v>
+      </c>
+      <c r="N1396" s="2" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="1397" spans="5:14">
+      <c r="E1397" t="s">
+        <v>5256</v>
+      </c>
+      <c r="F1397" t="s">
+        <v>5257</v>
+      </c>
+      <c r="G1397" t="s">
+        <v>5258</v>
+      </c>
+      <c r="H1397" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1397" t="s">
+        <v>5259</v>
+      </c>
+      <c r="J1397" t="s">
+        <v>5260</v>
+      </c>
+      <c r="M1397" t="s">
+        <v>975</v>
+      </c>
+      <c r="N1397" s="2" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="1398" spans="5:14">
+      <c r="E1398" t="s">
+        <v>5261</v>
+      </c>
+      <c r="F1398" t="s">
+        <v>5262</v>
+      </c>
+      <c r="G1398" t="s">
+        <v>5263</v>
+      </c>
+      <c r="H1398" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1398" t="s">
+        <v>5264</v>
+      </c>
+      <c r="J1398" t="s">
+        <v>5265</v>
+      </c>
+      <c r="M1398" t="s">
+        <v>975</v>
+      </c>
+      <c r="N1398" s="2" t="s">
+        <v>3318</v>
+      </c>
+    </row>
+    <row r="1399" spans="5:14">
+      <c r="E1399" t="s">
+        <v>976</v>
+      </c>
+      <c r="F1399" t="s">
+        <v>977</v>
+      </c>
+      <c r="G1399" t="s">
+        <v>5266</v>
+      </c>
+      <c r="H1399" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1399" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1399" t="s">
+        <v>980</v>
+      </c>
+      <c r="M1399" t="s">
+        <v>250</v>
+      </c>
+      <c r="N1399" s="2" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="1400" spans="5:14">
+      <c r="E1400" t="s">
+        <v>982</v>
+      </c>
+      <c r="F1400" t="s">
+        <v>983</v>
+      </c>
+      <c r="G1400" t="s">
+        <v>5266</v>
+      </c>
+      <c r="H1400" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1400" t="s">
+        <v>5267</v>
+      </c>
+      <c r="J1400" t="s">
+        <v>985</v>
+      </c>
+      <c r="M1400" t="s">
+        <v>250</v>
+      </c>
+      <c r="N1400" s="2" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="1401" spans="5:14">
+      <c r="E1401" t="s">
+        <v>969</v>
+      </c>
+      <c r="F1401" t="s">
+        <v>970</v>
+      </c>
+      <c r="G1401" t="s">
+        <v>5268</v>
+      </c>
+      <c r="H1401" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1401" t="s">
+        <v>5216</v>
+      </c>
+      <c r="J1401" t="s">
+        <v>974</v>
+      </c>
+      <c r="M1401" t="s">
+        <v>975</v>
+      </c>
+      <c r="N1401" s="2" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="1402" spans="5:14">
+      <c r="E1402" t="s">
+        <v>5269</v>
+      </c>
+      <c r="F1402" t="s">
+        <v>5270</v>
+      </c>
+      <c r="G1402" t="s">
+        <v>5268</v>
+      </c>
+      <c r="H1402" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1402" t="s">
+        <v>5271</v>
+      </c>
+      <c r="J1402" t="s">
+        <v>5272</v>
+      </c>
+      <c r="M1402" t="s">
+        <v>975</v>
+      </c>
+      <c r="N1402" s="2" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="1403" spans="5:14">
+      <c r="E1403" t="s">
+        <v>950</v>
+      </c>
+      <c r="F1403" t="s">
+        <v>951</v>
+      </c>
+      <c r="G1403" t="s">
+        <v>5273</v>
+      </c>
+      <c r="H1403" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1403" t="s">
+        <v>5274</v>
+      </c>
+      <c r="J1403" t="s">
+        <v>955</v>
+      </c>
+      <c r="M1403" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1403" s="2" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="1404" spans="5:14">
+      <c r="E1404" t="s">
+        <v>1763</v>
+      </c>
+      <c r="F1404" t="s">
+        <v>1764</v>
+      </c>
+      <c r="G1404" t="s">
+        <v>1765</v>
+      </c>
+      <c r="H1404" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1404" t="s">
+        <v>5275</v>
+      </c>
+      <c r="J1404" t="s">
+        <v>1766</v>
+      </c>
+      <c r="M1404" t="s">
+        <v>250</v>
+      </c>
+      <c r="N1404" s="2" t="s">
+        <v>5276</v>
+      </c>
+    </row>
+    <row r="1405" spans="5:14">
+      <c r="E1405" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F1405" t="s">
+        <v>5277</v>
+      </c>
+      <c r="G1405" t="s">
+        <v>2165</v>
+      </c>
+      <c r="H1405" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1405" t="s">
+        <v>2166</v>
+      </c>
+      <c r="J1405" t="s">
+        <v>2167</v>
+      </c>
+      <c r="M1405" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1405" s="2" t="s">
+        <v>5276</v>
+      </c>
+    </row>
+    <row r="1406" spans="5:14">
+      <c r="E1406" t="s">
+        <v>5278</v>
+      </c>
+      <c r="F1406" t="s">
+        <v>5279</v>
+      </c>
+      <c r="G1406" t="s">
+        <v>5280</v>
+      </c>
+      <c r="H1406" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1406" t="s">
+        <v>5281</v>
+      </c>
+      <c r="J1406" t="s">
+        <v>5282</v>
+      </c>
+      <c r="M1406" t="s">
+        <v>5283</v>
+      </c>
+      <c r="N1406" s="2" t="s">
+        <v>5276</v>
+      </c>
+    </row>
+    <row r="1407" spans="5:14">
+      <c r="E1407" t="s">
+        <v>2169</v>
+      </c>
+      <c r="F1407" t="s">
+        <v>2170</v>
+      </c>
+      <c r="G1407" t="s">
+        <v>2171</v>
+      </c>
+      <c r="H1407" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1407" t="s">
+        <v>5284</v>
+      </c>
+      <c r="J1407" t="s">
+        <v>2173</v>
+      </c>
+      <c r="M1407" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1407" s="2" t="s">
+        <v>5276</v>
+      </c>
+    </row>
+    <row r="1408" spans="5:14">
+      <c r="E1408" t="s">
+        <v>5285</v>
+      </c>
+      <c r="F1408" t="s">
+        <v>5286</v>
+      </c>
+      <c r="G1408" t="s">
+        <v>5287</v>
+      </c>
+      <c r="H1408" s="1" t="s">
+        <v>4165</v>
+      </c>
+      <c r="I1408" t="s">
+        <v>5288</v>
+      </c>
+      <c r="J1408" t="s">
+        <v>5289</v>
+      </c>
+      <c r="M1408" t="s">
+        <v>111</v>
+      </c>
+      <c r="N1408" s="2" t="s">
+        <v>5276</v>
+      </c>
+    </row>
+    <row r="1409" spans="5:14">
+      <c r="E1409" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F1409" t="s">
+        <v>2272</v>
+      </c>
+      <c r="G1409" t="s">
+        <v>2273</v>
+      </c>
+      <c r="H1409" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1409" t="s">
+        <v>5290</v>
+      </c>
+      <c r="J1409" t="s">
+        <v>2275</v>
+      </c>
+      <c r="M1409" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1409" s="2" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1410" spans="5:14">
+      <c r="E1410" t="s">
+        <v>5291</v>
+      </c>
+      <c r="F1410" t="s">
+        <v>5292</v>
+      </c>
+      <c r="G1410" t="s">
+        <v>5293</v>
+      </c>
+      <c r="H1410" s="1" t="s">
+        <v>5294</v>
+      </c>
+      <c r="I1410" t="s">
+        <v>5295</v>
+      </c>
+      <c r="J1410" t="s">
+        <v>5296</v>
+      </c>
+      <c r="M1410" t="s">
+        <v>5297</v>
+      </c>
+      <c r="N1410" s="2" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1411" spans="5:14">
+      <c r="E1411" t="s">
+        <v>2277</v>
+      </c>
+      <c r="F1411" t="s">
+        <v>2278</v>
+      </c>
+      <c r="G1411" t="s">
+        <v>2279</v>
+      </c>
+      <c r="H1411" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1411" t="s">
+        <v>701</v>
+      </c>
+      <c r="J1411" t="s">
+        <v>2281</v>
+      </c>
+      <c r="M1411" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1411" s="2" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1412" spans="5:14">
+      <c r="E1412" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F1412" t="s">
+        <v>2283</v>
+      </c>
+      <c r="G1412" t="s">
+        <v>2273</v>
+      </c>
+      <c r="H1412" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1412" t="s">
+        <v>2423</v>
+      </c>
+      <c r="J1412" t="s">
+        <v>2285</v>
+      </c>
+      <c r="M1412" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1412" s="2" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1413" spans="5:14">
+      <c r="E1413" t="s">
+        <v>5298</v>
+      </c>
+      <c r="F1413" t="s">
+        <v>5299</v>
+      </c>
+      <c r="G1413" t="s">
+        <v>5300</v>
+      </c>
+      <c r="H1413" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1413" t="s">
+        <v>5301</v>
+      </c>
+      <c r="J1413" t="s">
+        <v>5302</v>
+      </c>
+      <c r="M1413" t="s">
+        <v>5303</v>
+      </c>
+      <c r="N1413" s="2" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1414" spans="5:14">
+      <c r="E1414" t="s">
+        <v>5304</v>
+      </c>
+      <c r="F1414" t="s">
+        <v>5305</v>
+      </c>
+      <c r="G1414" t="s">
+        <v>5306</v>
+      </c>
+      <c r="H1414" s="1" t="s">
+        <v>1784</v>
+      </c>
+      <c r="I1414" t="s">
+        <v>5307</v>
+      </c>
+      <c r="J1414" t="s">
+        <v>5308</v>
+      </c>
+      <c r="M1414" t="s">
+        <v>5303</v>
+      </c>
+      <c r="N1414" s="2" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="1415" spans="5:14">
+      <c r="E1415" t="s">
+        <v>5309</v>
+      </c>
+      <c r="F1415" t="s">
+        <v>5310</v>
+      </c>
+      <c r="G1415" t="s">
+        <v>2709</v>
+      </c>
+      <c r="H1415" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1415" t="s">
+        <v>5311</v>
+      </c>
+      <c r="J1415" t="s">
+        <v>5312</v>
+      </c>
+      <c r="M1415" t="s">
+        <v>5313</v>
+      </c>
+      <c r="N1415" s="2" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="1416" spans="5:14">
+      <c r="E1416" t="s">
+        <v>5314</v>
+      </c>
+      <c r="F1416" t="s">
+        <v>5315</v>
+      </c>
+      <c r="G1416" t="s">
+        <v>2709</v>
+      </c>
+      <c r="H1416" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1416" t="s">
+        <v>5316</v>
+      </c>
+      <c r="J1416" t="s">
+        <v>5317</v>
+      </c>
+      <c r="M1416" t="s">
+        <v>975</v>
+      </c>
+      <c r="N1416" s="2" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="1417" spans="5:14">
+      <c r="E1417" t="s">
+        <v>5318</v>
+      </c>
+      <c r="F1417" t="s">
+        <v>5319</v>
+      </c>
+      <c r="G1417" t="s">
+        <v>5320</v>
+      </c>
+      <c r="H1417" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1417" t="s">
+        <v>5321</v>
+      </c>
+      <c r="J1417" t="s">
+        <v>5322</v>
+      </c>
+      <c r="M1417" t="s">
+        <v>5323</v>
+      </c>
+      <c r="N1417" s="2" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="1418" spans="5:14">
+      <c r="E1418" t="s">
+        <v>5324</v>
+      </c>
+      <c r="F1418" t="s">
+        <v>5325</v>
+      </c>
+      <c r="G1418" t="s">
+        <v>5320</v>
+      </c>
+      <c r="H1418" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1418" t="s">
+        <v>5311</v>
+      </c>
+      <c r="J1418" t="s">
+        <v>5326</v>
+      </c>
+      <c r="M1418" t="s">
+        <v>5327</v>
+      </c>
+      <c r="N1418" s="2" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="1419" spans="5:14">
+      <c r="E1419" t="s">
+        <v>5328</v>
+      </c>
+      <c r="F1419" t="s">
+        <v>5329</v>
+      </c>
+      <c r="G1419" t="s">
+        <v>5320</v>
+      </c>
+      <c r="H1419" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1419" t="s">
+        <v>1174</v>
+      </c>
+      <c r="J1419" t="s">
+        <v>5330</v>
+      </c>
+      <c r="M1419" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1419" s="2" t="s">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="1420" spans="5:14">
+      <c r="E1420" t="s">
+        <v>2841</v>
+      </c>
+      <c r="F1420" t="s">
+        <v>2842</v>
+      </c>
+      <c r="G1420" t="s">
+        <v>5331</v>
+      </c>
+      <c r="H1420" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1420" t="s">
+        <v>5332</v>
+      </c>
+      <c r="J1420" t="s">
+        <v>2844</v>
+      </c>
+      <c r="M1420" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1420" s="2" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="1421" spans="5:14">
+      <c r="E1421" t="s">
+        <v>2850</v>
+      </c>
+      <c r="F1421" t="s">
+        <v>2851</v>
+      </c>
+      <c r="G1421" t="s">
+        <v>5333</v>
+      </c>
+      <c r="H1421" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1421" t="s">
+        <v>5334</v>
+      </c>
+      <c r="J1421" t="s">
+        <v>2853</v>
+      </c>
+      <c r="M1421" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1421" s="2" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="1422" spans="5:14">
+      <c r="E1422" t="s">
+        <v>5335</v>
+      </c>
+      <c r="F1422" t="s">
+        <v>5336</v>
+      </c>
+      <c r="G1422" t="s">
+        <v>5337</v>
+      </c>
+      <c r="H1422" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="I1422" t="s">
+        <v>5338</v>
+      </c>
+      <c r="J1422" t="s">
+        <v>5339</v>
+      </c>
+      <c r="M1422" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1422" s="2" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="1423" spans="5:14">
+      <c r="E1423" t="s">
+        <v>5340</v>
+      </c>
+      <c r="F1423" t="s">
+        <v>5341</v>
+      </c>
+      <c r="G1423" t="s">
+        <v>5342</v>
+      </c>
+      <c r="H1423" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1423" t="s">
+        <v>5343</v>
+      </c>
+      <c r="J1423" t="s">
+        <v>5344</v>
+      </c>
+      <c r="M1423" t="s">
+        <v>5345</v>
+      </c>
+      <c r="N1423" s="2" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="1424" spans="5:14">
+      <c r="E1424" t="s">
+        <v>5346</v>
+      </c>
+      <c r="F1424" t="s">
+        <v>5347</v>
+      </c>
+      <c r="G1424" t="s">
+        <v>5348</v>
+      </c>
+      <c r="H1424" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1424" t="s">
+        <v>5349</v>
+      </c>
+      <c r="J1424" t="s">
+        <v>5350</v>
+      </c>
+      <c r="M1424" t="s">
+        <v>1653</v>
+      </c>
+      <c r="N1424" s="2" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="1425" spans="5:14">
+      <c r="E1425" t="s">
+        <v>5351</v>
+      </c>
+      <c r="F1425" t="s">
+        <v>5352</v>
+      </c>
+      <c r="G1425" t="s">
+        <v>5353</v>
+      </c>
+      <c r="H1425" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="I1425" t="s">
+        <v>5354</v>
+      </c>
+      <c r="J1425" t="s">
+        <v>5355</v>
+      </c>
+      <c r="M1425" t="s">
+        <v>5345</v>
+      </c>
+      <c r="N1425" s="2" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="1426" spans="5:14">
+      <c r="E1426" t="s">
+        <v>3264</v>
+      </c>
+      <c r="F1426" t="s">
+        <v>3265</v>
+      </c>
+      <c r="G1426" t="s">
+        <v>3266</v>
+      </c>
+      <c r="H1426" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1426" t="s">
+        <v>5356</v>
+      </c>
+      <c r="J1426" t="s">
+        <v>3268</v>
+      </c>
+      <c r="M1426" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1426" s="2" t="s">
+        <v>5357</v>
+      </c>
+    </row>
+    <row r="1427" spans="5:14">
+      <c r="E1427" t="s">
+        <v>2845</v>
+      </c>
+      <c r="F1427" t="s">
+        <v>2846</v>
+      </c>
+      <c r="G1427" t="s">
+        <v>2847</v>
+      </c>
+      <c r="H1427" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1427" t="s">
+        <v>5358</v>
+      </c>
+      <c r="J1427" t="s">
+        <v>2849</v>
+      </c>
+      <c r="M1427" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1427" s="2" t="s">
+        <v>5357</v>
+      </c>
+    </row>
+    <row r="1428" spans="5:14">
+      <c r="E1428" t="s">
+        <v>3279</v>
+      </c>
+      <c r="F1428" t="s">
+        <v>5359</v>
+      </c>
+      <c r="G1428" t="s">
+        <v>3281</v>
+      </c>
+      <c r="H1428" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1428" t="s">
+        <v>5360</v>
+      </c>
+      <c r="J1428" t="s">
+        <v>3283</v>
+      </c>
+      <c r="M1428" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1428" s="2" t="s">
+        <v>5357</v>
+      </c>
+    </row>
+    <row r="1429" spans="5:14">
+      <c r="E1429" t="s">
+        <v>3284</v>
+      </c>
+      <c r="F1429" t="s">
+        <v>3285</v>
+      </c>
+      <c r="G1429" t="s">
+        <v>3286</v>
+      </c>
+      <c r="H1429" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1429" t="s">
+        <v>5361</v>
+      </c>
+      <c r="J1429" t="s">
+        <v>3288</v>
+      </c>
+      <c r="M1429" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1429" s="2" t="s">
+        <v>5357</v>
+      </c>
+    </row>
+    <row r="1430" spans="5:14">
+      <c r="E1430" t="s">
+        <v>3289</v>
+      </c>
+      <c r="F1430" t="s">
+        <v>3290</v>
+      </c>
+      <c r="G1430" t="s">
+        <v>3291</v>
+      </c>
+      <c r="H1430" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1430" t="s">
+        <v>5362</v>
+      </c>
+      <c r="J1430" t="s">
+        <v>3293</v>
+      </c>
+      <c r="M1430" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1430" s="2" t="s">
+        <v>5357</v>
+      </c>
+    </row>
+    <row r="1431" spans="5:14">
+      <c r="E1431" t="s">
+        <v>580</v>
+      </c>
+      <c r="F1431" t="s">
+        <v>581</v>
+      </c>
+      <c r="G1431" t="s">
+        <v>582</v>
+      </c>
+      <c r="H1431" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="I1431" t="s">
+        <v>5363</v>
+      </c>
+      <c r="J1431" t="s">
+        <v>585</v>
+      </c>
+      <c r="M1431" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1431" s="2" t="s">
+        <v>5364</v>
+      </c>
+    </row>
+    <row r="1432" spans="5:14">
+      <c r="E1432" t="s">
+        <v>4775</v>
+      </c>
+      <c r="F1432" t="s">
+        <v>4776</v>
+      </c>
+      <c r="G1432" t="s">
+        <v>4777</v>
+      </c>
+      <c r="H1432" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I1432" t="s">
+        <v>5365</v>
+      </c>
+      <c r="J1432" t="s">
+        <v>4778</v>
+      </c>
+      <c r="M1432" t="s">
+        <v>250</v>
+      </c>
+      <c r="N1432" s="2" t="s">
+        <v>5364</v>
+      </c>
+    </row>
+    <row r="1433" spans="5:14">
+      <c r="E1433" t="s">
+        <v>604</v>
+      </c>
+      <c r="F1433" t="s">
+        <v>605</v>
+      </c>
+      <c r="G1433" t="s">
+        <v>606</v>
+      </c>
+      <c r="H1433" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1433" t="s">
+        <v>5311</v>
+      </c>
+      <c r="J1433" t="s">
+        <v>608</v>
+      </c>
+      <c r="M1433" t="s">
+        <v>5366</v>
+      </c>
+      <c r="N1433" s="2" t="s">
+        <v>5364</v>
+      </c>
+    </row>
+    <row r="1434" spans="5:14">
+      <c r="E1434" t="s">
+        <v>5367</v>
+      </c>
+      <c r="F1434" t="s">
+        <v>5368</v>
+      </c>
+      <c r="G1434" t="s">
+        <v>5369</v>
+      </c>
+      <c r="H1434" s="1" t="s">
+        <v>3387</v>
+      </c>
+      <c r="I1434" t="s">
+        <v>5370</v>
+      </c>
+      <c r="J1434" t="s">
+        <v>5371</v>
+      </c>
+      <c r="M1434" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1434" s="2" t="s">
+        <v>5364</v>
+      </c>
+    </row>
+    <row r="1435" spans="5:14">
+      <c r="E1435" t="s">
+        <v>5372</v>
+      </c>
+      <c r="F1435" t="s">
+        <v>5373</v>
+      </c>
+      <c r="G1435" t="s">
+        <v>5374</v>
+      </c>
+      <c r="H1435" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I1435" t="s">
+        <v>5375</v>
+      </c>
+      <c r="J1435" t="s">
+        <v>5376</v>
+      </c>
+      <c r="M1435" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1435" s="2" t="s">
+        <v>5364</v>
+      </c>
+    </row>
+    <row r="1436" spans="5:14">
+      <c r="E1436" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F1436" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G1436" t="s">
+        <v>5377</v>
+      </c>
+      <c r="H1436" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1436" t="s">
+        <v>5378</v>
+      </c>
+      <c r="J1436" t="s">
+        <v>1709</v>
+      </c>
+      <c r="M1436" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1436" s="2" t="s">
+        <v>5379</v>
+      </c>
+    </row>
+    <row r="1437" spans="5:14">
+      <c r="E1437" t="s">
+        <v>1710</v>
+      </c>
+      <c r="F1437" t="s">
+        <v>1711</v>
+      </c>
+      <c r="G1437" t="s">
+        <v>5380</v>
+      </c>
+      <c r="H1437" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1437" t="s">
+        <v>307</v>
+      </c>
+      <c r="J1437" t="s">
+        <v>1714</v>
+      </c>
+      <c r="M1437" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1437" s="2" t="s">
+        <v>5379</v>
+      </c>
+    </row>
+    <row r="1438" spans="5:14">
+      <c r="E1438" t="s">
+        <v>934</v>
+      </c>
+      <c r="F1438" t="s">
+        <v>935</v>
+      </c>
+      <c r="G1438" t="s">
+        <v>936</v>
+      </c>
+      <c r="H1438" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1438" t="s">
+        <v>5381</v>
+      </c>
+      <c r="J1438" t="s">
+        <v>938</v>
+      </c>
+      <c r="M1438" t="s">
+        <v>5382</v>
+      </c>
+      <c r="N1438" s="2" t="s">
+        <v>5383</v>
+      </c>
+    </row>
+    <row r="1439" spans="5:14">
+      <c r="E1439" t="s">
+        <v>5384</v>
+      </c>
+      <c r="F1439" t="s">
+        <v>944</v>
+      </c>
+      <c r="G1439" t="s">
+        <v>930</v>
+      </c>
+      <c r="H1439" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1439" t="s">
+        <v>5385</v>
+      </c>
+      <c r="J1439" t="s">
+        <v>946</v>
+      </c>
+      <c r="M1439" t="s">
+        <v>5386</v>
+      </c>
+      <c r="N1439" s="2" t="s">
+        <v>5383</v>
+      </c>
+    </row>
+    <row r="1440" spans="5:14">
+      <c r="E1440" t="s">
+        <v>5387</v>
+      </c>
+      <c r="F1440" t="s">
+        <v>5388</v>
+      </c>
+      <c r="G1440" t="s">
+        <v>5389</v>
+      </c>
+      <c r="H1440" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1440" t="s">
+        <v>5390</v>
+      </c>
+      <c r="J1440" t="s">
+        <v>5391</v>
+      </c>
+      <c r="M1440" t="s">
+        <v>5392</v>
+      </c>
+      <c r="N1440" s="2" t="s">
+        <v>5383</v>
+      </c>
+    </row>
+    <row r="1441" spans="5:14">
+      <c r="E1441" t="s">
+        <v>5393</v>
+      </c>
+      <c r="F1441" t="s">
+        <v>5394</v>
+      </c>
+      <c r="G1441" t="s">
+        <v>5395</v>
+      </c>
+      <c r="H1441" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1441" t="s">
+        <v>5396</v>
+      </c>
+      <c r="J1441" t="s">
+        <v>5397</v>
+      </c>
+      <c r="M1441" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1441" s="2" t="s">
+        <v>5383</v>
+      </c>
+    </row>
+    <row r="1442" spans="5:14">
+      <c r="E1442" t="s">
+        <v>5398</v>
+      </c>
+      <c r="F1442" t="s">
+        <v>5399</v>
+      </c>
+      <c r="G1442" t="s">
+        <v>930</v>
+      </c>
+      <c r="H1442" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1442" t="s">
+        <v>5400</v>
+      </c>
+      <c r="J1442" t="s">
+        <v>5401</v>
+      </c>
+      <c r="M1442" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1442" s="2" t="s">
+        <v>5383</v>
+      </c>
+    </row>
+    <row r="1443" spans="5:14">
+      <c r="E1443" t="s">
+        <v>5402</v>
+      </c>
+      <c r="F1443" t="s">
+        <v>5403</v>
+      </c>
+      <c r="G1443" t="s">
+        <v>5404</v>
+      </c>
+      <c r="H1443" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1443" t="s">
+        <v>5405</v>
+      </c>
+      <c r="J1443" t="s">
+        <v>5406</v>
+      </c>
+      <c r="M1443" t="s">
+        <v>1653</v>
+      </c>
+      <c r="N1443" s="2" t="s">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="1444" spans="5:14">
+      <c r="E1444" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F1444" t="s">
+        <v>1213</v>
+      </c>
+      <c r="G1444" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H1444" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1444" t="s">
+        <v>5407</v>
+      </c>
+      <c r="J1444" t="s">
+        <v>1216</v>
+      </c>
+      <c r="M1444" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1444" s="2" t="s">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="1445" spans="5:14">
+      <c r="E1445" t="s">
+        <v>5408</v>
+      </c>
+      <c r="F1445" t="s">
+        <v>5409</v>
+      </c>
+      <c r="G1445" t="s">
+        <v>5410</v>
+      </c>
+      <c r="H1445" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1445" t="s">
+        <v>3622</v>
+      </c>
+      <c r="J1445" t="s">
+        <v>5411</v>
+      </c>
+      <c r="M1445" t="s">
+        <v>1653</v>
+      </c>
+      <c r="N1445" s="2" t="s">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="1446" spans="5:14">
+      <c r="E1446" t="s">
+        <v>5412</v>
+      </c>
+      <c r="F1446" t="s">
+        <v>5413</v>
+      </c>
+      <c r="G1446" t="s">
+        <v>5414</v>
+      </c>
+      <c r="H1446" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1446" t="s">
+        <v>3622</v>
+      </c>
+      <c r="J1446" t="s">
+        <v>5415</v>
+      </c>
+      <c r="M1446" t="s">
+        <v>1653</v>
+      </c>
+      <c r="N1446" s="2" t="s">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="1447" spans="5:14">
+      <c r="E1447" t="s">
+        <v>5416</v>
+      </c>
+      <c r="F1447" t="s">
+        <v>5417</v>
+      </c>
+      <c r="G1447" t="s">
+        <v>5418</v>
+      </c>
+      <c r="H1447" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1447" t="s">
+        <v>3622</v>
+      </c>
+      <c r="J1447" t="s">
+        <v>5419</v>
+      </c>
+      <c r="M1447" t="s">
+        <v>1653</v>
+      </c>
+      <c r="N1447" s="2" t="s">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="1448" spans="5:14">
+      <c r="E1448" t="s">
+        <v>5420</v>
+      </c>
+      <c r="F1448" t="s">
+        <v>5421</v>
+      </c>
+      <c r="G1448" t="s">
+        <v>5422</v>
+      </c>
+      <c r="H1448" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1448" t="s">
+        <v>1664</v>
+      </c>
+      <c r="J1448" t="s">
+        <v>5423</v>
+      </c>
+      <c r="M1448" t="s">
+        <v>2321</v>
+      </c>
+      <c r="N1448" s="2" t="s">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="1449" spans="5:14">
+      <c r="E1449" t="s">
+        <v>5424</v>
+      </c>
+      <c r="F1449" t="s">
+        <v>5425</v>
+      </c>
+      <c r="G1449" t="s">
+        <v>5426</v>
+      </c>
+      <c r="H1449" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1449" t="s">
+        <v>208</v>
+      </c>
+      <c r="J1449" t="s">
+        <v>5427</v>
+      </c>
+      <c r="M1449" t="s">
+        <v>2321</v>
+      </c>
+      <c r="N1449" s="2" t="s">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="1450" spans="5:14">
+      <c r="E1450" t="s">
+        <v>3783</v>
+      </c>
+      <c r="F1450" t="s">
+        <v>3784</v>
+      </c>
+      <c r="G1450" t="s">
+        <v>3785</v>
+      </c>
+      <c r="H1450" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1450" t="s">
+        <v>408</v>
+      </c>
+      <c r="J1450" t="s">
+        <v>5428</v>
+      </c>
+      <c r="M1450" t="s">
+        <v>2321</v>
+      </c>
+      <c r="N1450" s="2" t="s">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="1451" spans="5:14">
+      <c r="E1451" t="s">
+        <v>3787</v>
+      </c>
+      <c r="F1451" t="s">
+        <v>3788</v>
+      </c>
+      <c r="G1451" t="s">
+        <v>3789</v>
+      </c>
+      <c r="H1451" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1451" t="s">
+        <v>408</v>
+      </c>
+      <c r="J1451" t="s">
+        <v>5429</v>
+      </c>
+      <c r="M1451" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1451" s="2" t="s">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="1452" spans="5:14">
+      <c r="E1452" t="s">
+        <v>3791</v>
+      </c>
+      <c r="F1452" t="s">
+        <v>3792</v>
+      </c>
+      <c r="G1452" t="s">
+        <v>3793</v>
+      </c>
+      <c r="H1452" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1452" t="s">
+        <v>2153</v>
+      </c>
+      <c r="J1452" t="s">
+        <v>5430</v>
+      </c>
+      <c r="M1452" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1452" s="2" t="s">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="1453" spans="5:14">
+      <c r="E1453" t="s">
+        <v>3847</v>
+      </c>
+      <c r="F1453" t="s">
+        <v>3848</v>
+      </c>
+      <c r="G1453" t="s">
+        <v>3849</v>
+      </c>
+      <c r="H1453" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1453" t="s">
+        <v>5431</v>
+      </c>
+      <c r="J1453" t="s">
+        <v>3851</v>
+      </c>
+      <c r="M1453" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1453" s="2" t="s">
+        <v>3852</v>
+      </c>
+    </row>
+    <row r="1454" spans="5:14">
+      <c r="E1454" t="s">
+        <v>3853</v>
+      </c>
+      <c r="F1454" t="s">
+        <v>3854</v>
+      </c>
+      <c r="G1454" t="s">
+        <v>3849</v>
+      </c>
+      <c r="H1454" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1454" t="s">
+        <v>3805</v>
+      </c>
+      <c r="J1454" t="s">
+        <v>3851</v>
+      </c>
+      <c r="M1454" t="s">
+        <v>111</v>
+      </c>
+      <c r="N1454" s="2" t="s">
+        <v>3852</v>
+      </c>
+    </row>
+    <row r="1455" spans="5:14">
+      <c r="E1455" t="s">
+        <v>3856</v>
+      </c>
+      <c r="F1455" t="s">
+        <v>3857</v>
+      </c>
+      <c r="G1455" t="s">
+        <v>3849</v>
+      </c>
+      <c r="H1455" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1455" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1455" t="s">
+        <v>3851</v>
+      </c>
+      <c r="M1455" t="s">
+        <v>3859</v>
+      </c>
+      <c r="N1455" s="2" t="s">
+        <v>3852</v>
+      </c>
+    </row>
+    <row r="1456" spans="5:14">
+      <c r="E1456" t="s">
+        <v>3860</v>
+      </c>
+      <c r="F1456" t="s">
+        <v>3861</v>
+      </c>
+      <c r="G1456" t="s">
+        <v>3849</v>
+      </c>
+      <c r="H1456" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1456" t="s">
+        <v>3862</v>
+      </c>
+      <c r="J1456" t="s">
+        <v>3851</v>
+      </c>
+      <c r="M1456" t="s">
+        <v>3859</v>
+      </c>
+      <c r="N1456" s="2" t="s">
+        <v>3852</v>
+      </c>
+    </row>
+    <row r="1457" spans="5:14">
+      <c r="E1457" t="s">
+        <v>3863</v>
+      </c>
+      <c r="F1457" t="s">
+        <v>3864</v>
+      </c>
+      <c r="G1457" t="s">
+        <v>3849</v>
+      </c>
+      <c r="H1457" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1457" t="s">
+        <v>2469</v>
+      </c>
+      <c r="J1457" t="s">
+        <v>3851</v>
+      </c>
+      <c r="M1457" t="s">
+        <v>3859</v>
+      </c>
+      <c r="N1457" s="2" t="s">
+        <v>3852</v>
+      </c>
+    </row>
+    <row r="1458" spans="5:14">
+      <c r="E1458" t="s">
+        <v>5432</v>
+      </c>
+      <c r="F1458" t="s">
+        <v>5433</v>
+      </c>
+      <c r="G1458" t="s">
+        <v>5434</v>
+      </c>
+      <c r="H1458" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1458" t="s">
+        <v>4858</v>
+      </c>
+      <c r="J1458" t="s">
+        <v>5435</v>
+      </c>
+      <c r="M1458" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1458" s="2" t="s">
+        <v>4845</v>
+      </c>
+    </row>
+    <row r="1459" spans="5:14">
+      <c r="E1459" t="s">
+        <v>5436</v>
+      </c>
+      <c r="F1459" t="s">
+        <v>5437</v>
+      </c>
+      <c r="G1459" t="s">
+        <v>5438</v>
+      </c>
+      <c r="H1459" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1459" t="s">
+        <v>4858</v>
+      </c>
+      <c r="J1459" t="s">
+        <v>5439</v>
+      </c>
+      <c r="M1459" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1459" s="2" t="s">
+        <v>4845</v>
+      </c>
+    </row>
+    <row r="1460" spans="5:14">
+      <c r="E1460" t="s">
+        <v>5440</v>
+      </c>
+      <c r="F1460" t="s">
+        <v>5441</v>
+      </c>
+      <c r="G1460" t="s">
+        <v>5442</v>
+      </c>
+      <c r="H1460" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1460" t="s">
+        <v>5378</v>
+      </c>
+      <c r="J1460" t="s">
+        <v>5443</v>
+      </c>
+      <c r="M1460" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1460" s="2" t="s">
+        <v>4845</v>
+      </c>
+    </row>
+    <row r="1461" spans="5:14">
+      <c r="E1461" t="s">
+        <v>5444</v>
+      </c>
+      <c r="F1461" t="s">
+        <v>5445</v>
+      </c>
+      <c r="G1461" t="s">
+        <v>5446</v>
+      </c>
+      <c r="H1461" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1461" t="s">
+        <v>4853</v>
+      </c>
+      <c r="J1461" t="s">
+        <v>5447</v>
+      </c>
+      <c r="M1461" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1461" s="2" t="s">
+        <v>4845</v>
+      </c>
+    </row>
+    <row r="1462" spans="5:14">
+      <c r="E1462" t="s">
+        <v>5448</v>
+      </c>
+      <c r="F1462" t="s">
+        <v>5449</v>
+      </c>
+      <c r="G1462" t="s">
+        <v>5450</v>
+      </c>
+      <c r="H1462" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I1462" t="s">
+        <v>2803</v>
+      </c>
+      <c r="J1462" t="s">
+        <v>5451</v>
+      </c>
+      <c r="M1462" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1462" s="2" t="s">
+        <v>4845</v>
+      </c>
+    </row>
+    <row r="1464" spans="5:14">
+      <c r="E1464" t="s">
+        <v>1929</v>
+      </c>
+      <c r="F1464" t="s">
+        <v>1930</v>
+      </c>
+      <c r="G1464" t="s">
+        <v>1931</v>
+      </c>
+      <c r="H1464" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1464" t="s">
+        <v>5452</v>
+      </c>
+      <c r="J1464" t="s">
+        <v>1933</v>
+      </c>
+      <c r="M1464" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1464" s="2" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="1465" spans="5:14">
+      <c r="E1465" t="s">
+        <v>1935</v>
+      </c>
+      <c r="F1465" t="s">
+        <v>1936</v>
+      </c>
+      <c r="G1465" t="s">
+        <v>1937</v>
+      </c>
+      <c r="H1465" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1465" t="s">
+        <v>1938</v>
+      </c>
+      <c r="J1465" t="s">
+        <v>1939</v>
+      </c>
+      <c r="M1465" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1465" s="2" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="1466" spans="5:14">
+      <c r="E1466" t="s">
+        <v>1940</v>
+      </c>
+      <c r="F1466" t="s">
+        <v>1941</v>
+      </c>
+      <c r="G1466" t="s">
+        <v>1942</v>
+      </c>
+      <c r="H1466" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1466" t="s">
+        <v>712</v>
+      </c>
+      <c r="J1466" t="s">
+        <v>1943</v>
+      </c>
+      <c r="M1466" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1466" s="2" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="1467" spans="5:14">
+      <c r="E1467" t="s">
+        <v>1944</v>
+      </c>
+      <c r="F1467" t="s">
+        <v>1945</v>
+      </c>
+      <c r="G1467" t="s">
+        <v>1946</v>
+      </c>
+      <c r="H1467" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1467" t="s">
+        <v>3901</v>
+      </c>
+      <c r="J1467" t="s">
+        <v>1948</v>
+      </c>
+      <c r="M1467" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1467" s="2" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="1468" spans="5:14">
+      <c r="E1468" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F1468" t="s">
+        <v>1951</v>
+      </c>
+      <c r="G1468" t="s">
+        <v>1952</v>
+      </c>
+      <c r="H1468" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1468" t="s">
+        <v>5453</v>
+      </c>
+      <c r="J1468" t="s">
+        <v>1953</v>
+      </c>
+      <c r="M1468" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1468" s="2" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="1469" spans="5:14">
+      <c r="E1469" t="s">
+        <v>1954</v>
+      </c>
+      <c r="F1469" t="s">
+        <v>1955</v>
+      </c>
+      <c r="G1469" t="s">
+        <v>1956</v>
+      </c>
+      <c r="H1469" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I1469" t="s">
+        <v>5454</v>
+      </c>
+      <c r="J1469" t="s">
+        <v>1957</v>
+      </c>
+      <c r="M1469" t="s">
+        <v>5076</v>
+      </c>
+      <c r="N1469" s="2" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="1472" spans="5:14">
+      <c r="E1472" t="s">
+        <v>5455</v>
+      </c>
+      <c r="F1472" t="s">
+        <v>5456</v>
+      </c>
+      <c r="G1472" t="s">
+        <v>2821</v>
+      </c>
+      <c r="H1472" s="1" t="s">
+        <v>5457</v>
+      </c>
+      <c r="I1472" t="s">
+        <v>5458</v>
+      </c>
+      <c r="J1472" t="s">
+        <v>5459</v>
+      </c>
+      <c r="M1472" t="s">
+        <v>5460</v>
+      </c>
+      <c r="N1472" s="2" t="s">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="1473" spans="5:14">
+      <c r="E1473" t="s">
+        <v>5461</v>
+      </c>
+      <c r="F1473" t="s">
+        <v>5462</v>
+      </c>
+      <c r="G1473" t="s">
+        <v>2821</v>
+      </c>
+      <c r="H1473" s="1" t="s">
+        <v>5457</v>
+      </c>
+      <c r="I1473" t="s">
+        <v>5463</v>
+      </c>
+      <c r="J1473" t="s">
+        <v>5459</v>
+      </c>
+      <c r="M1473" t="s">
+        <v>5464</v>
+      </c>
+      <c r="N1473" s="2" t="s">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="1474" spans="5:14">
+      <c r="E1474" t="s">
+        <v>5465</v>
+      </c>
+      <c r="F1474" t="s">
+        <v>5466</v>
+      </c>
+      <c r="G1474" t="s">
+        <v>2821</v>
+      </c>
+      <c r="H1474" s="1" t="s">
+        <v>5457</v>
+      </c>
+      <c r="I1474" t="s">
+        <v>5467</v>
+      </c>
+      <c r="J1474" t="s">
+        <v>5459</v>
+      </c>
+      <c r="M1474" t="s">
+        <v>5468</v>
+      </c>
+      <c r="N1474" s="2" t="s">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="1475" spans="5:14">
+      <c r="E1475" t="s">
+        <v>5469</v>
+      </c>
+      <c r="F1475" t="s">
+        <v>5470</v>
+      </c>
+      <c r="G1475" t="s">
+        <v>2821</v>
+      </c>
+      <c r="H1475" s="1" t="s">
+        <v>5457</v>
+      </c>
+      <c r="I1475" t="s">
+        <v>5471</v>
+      </c>
+      <c r="J1475" t="s">
+        <v>5459</v>
+      </c>
+      <c r="M1475" t="s">
+        <v>5472</v>
+      </c>
+      <c r="N1475" s="2" t="s">
+        <v>2823</v>
       </c>
     </row>
   </sheetData>
@@ -50041,7 +54462,7 @@
         <v>989</v>
       </c>
       <c r="E37" t="s">
-        <v>5072</v>
+        <v>5473</v>
       </c>
       <c r="F37" t="s">
         <v>1859</v>
